--- a/ZR.Admin.WebApi/wwwroot/data.xlsx
+++ b/ZR.Admin.WebApi/wwwroot/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Mine\public\ZrAdminNet\ZR.Admin.WebApi\wwwroot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF64476A-BEA8-4DB3-8CF8-B6BE700D1C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED31845-7757-47B9-8FAF-89EBAAA0325E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="849" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,14 +29,14 @@
     <sheet name="notice" sheetId="13" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">menu!$A$1:$A$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">menu!$A$1:$A$126</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="814">
   <si>
     <t>系统管理</t>
   </si>
@@ -2742,6 +2742,59 @@
   </si>
   <si>
     <t>menu.systemUser</t>
+  </si>
+  <si>
+    <t>RouteName</t>
+  </si>
+  <si>
+    <t>规格模板管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spectpl:list</t>
+  </si>
+  <si>
+    <t>spectpl:add</t>
+  </si>
+  <si>
+    <t>spectpl:edit</t>
+  </si>
+  <si>
+    <t>spectpl:delete</t>
+  </si>
+  <si>
+    <t>添加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shopping/SpecTemplate</t>
+  </si>
+  <si>
+    <t>SpecTemplate</t>
+  </si>
+  <si>
+    <t>SpecTemplate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zujian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5258,7 +5311,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N175"/>
+  <dimension ref="A1:O179"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.4140625" customWidth="1"/>
@@ -5269,9 +5322,10 @@
     <col min="12" max="12" width="10.58203125" customWidth="1"/>
     <col min="13" max="13" width="18.4140625" customWidth="1"/>
     <col min="14" max="14" width="21.75" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>282</v>
       </c>
@@ -5314,8 +5368,11 @@
       <c r="N1" s="12" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -5353,7 +5410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>2</v>
       </c>
@@ -5391,7 +5448,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>3</v>
       </c>
@@ -5429,7 +5486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>5</v>
       </c>
@@ -5467,7 +5524,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>6</v>
       </c>
@@ -5507,7 +5564,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>7</v>
       </c>
@@ -5543,7 +5600,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>9</v>
       </c>
@@ -5581,7 +5638,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>8</v>
       </c>
@@ -5621,7 +5678,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>10</v>
       </c>
@@ -5663,50 +5720,54 @@
         <v>622</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>796</v>
+        <v>730</v>
       </c>
       <c r="C11" s="12">
         <v>0</v>
       </c>
       <c r="D11" s="12">
-        <v>9999</v>
-      </c>
-      <c r="E11" s="12"/>
+        <v>11</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>770</v>
+      </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>797</v>
+        <v>543</v>
       </c>
       <c r="I11" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="12">
         <v>0</v>
       </c>
       <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
+      <c r="L11" s="20" t="s">
+        <v>723</v>
+      </c>
       <c r="M11" s="12"/>
       <c r="N11" s="12"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="12">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C12" s="12">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D12" s="12">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -5714,29 +5775,25 @@
         <v>0</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>126</v>
+        <v>797</v>
       </c>
       <c r="I12" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="12">
         <v>0</v>
       </c>
-      <c r="K12" s="12" t="s">
-        <v>787</v>
-      </c>
+      <c r="K12" s="12"/>
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
-      <c r="N12" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N12" s="12"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="12">
-        <v>14</v>
+        <v>504</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C13" s="12">
         <v>12</v>
@@ -5759,18 +5816,20 @@
         <v>0</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="L13" s="12"/>
       <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N13" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="12">
-        <v>15</v>
+        <v>505</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C14" s="12">
         <v>12</v>
@@ -5784,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>793</v>
+        <v>126</v>
       </c>
       <c r="I14" s="12">
         <v>0</v>
@@ -5793,17 +5852,18 @@
         <v>0</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="L14" s="12"/>
       <c r="M14" s="12"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N14" s="12"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="12">
-        <v>16</v>
+        <v>506</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C15" s="12">
         <v>12</v>
@@ -5826,35 +5886,31 @@
         <v>0</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L15" s="12"/>
       <c r="M15" s="12"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="12">
-        <v>100</v>
+        <v>507</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>20</v>
+        <v>790</v>
       </c>
       <c r="C16" s="12">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D16" s="12">
         <v>1</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>22</v>
-      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
       <c r="G16" s="12">
         <v>0</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>17</v>
+        <v>793</v>
       </c>
       <c r="I16" s="12">
         <v>0</v>
@@ -5863,34 +5919,29 @@
         <v>0</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>21</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="L16" s="12"/>
       <c r="M16" s="12"/>
-      <c r="N16" s="12" t="s">
-        <v>798</v>
-      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="12">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C17" s="12">
         <v>1</v>
       </c>
       <c r="D17" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G17" s="12">
         <v>0</v>
@@ -5905,34 +5956,34 @@
         <v>0</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="M17" s="12"/>
       <c r="N17" s="12" t="s">
-        <v>29</v>
+        <v>798</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="12">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C18" s="12">
         <v>1</v>
       </c>
       <c r="D18" s="12">
-        <v>3</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>713</v>
+        <v>2</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G18" s="12">
         <v>0</v>
@@ -5947,34 +5998,34 @@
         <v>0</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M18" s="12"/>
       <c r="N18" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="12">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C19" s="12">
         <v>1</v>
       </c>
       <c r="D19" s="12">
-        <v>4</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>36</v>
+        <v>3</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>713</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G19" s="12">
         <v>0</v>
@@ -5989,34 +6040,34 @@
         <v>0</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="M19" s="12"/>
       <c r="N19" s="12" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="12">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C20" s="12">
         <v>1</v>
       </c>
       <c r="D20" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G20" s="12">
         <v>0</v>
@@ -6031,34 +6082,34 @@
         <v>0</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M20" s="12"/>
       <c r="N20" s="12" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="12">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C21" s="12">
         <v>1</v>
       </c>
       <c r="D21" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G21" s="12">
         <v>0</v>
@@ -6073,34 +6124,34 @@
         <v>0</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M21" s="12"/>
       <c r="N21" s="12" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="12">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C22" s="12">
         <v>1</v>
       </c>
       <c r="D22" s="12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G22" s="12">
         <v>0</v>
@@ -6109,38 +6160,40 @@
         <v>17</v>
       </c>
       <c r="I22" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="12">
         <v>0</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
+      <c r="N22" s="12" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="12">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C23" s="12">
         <v>1</v>
       </c>
       <c r="D23" s="12">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G23" s="12">
         <v>0</v>
@@ -6149,44 +6202,44 @@
         <v>17</v>
       </c>
       <c r="I23" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="12">
         <v>0</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M23" s="12"/>
-      <c r="N23" s="12" t="s">
-        <v>61</v>
-      </c>
+      <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="12">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C24" s="12">
         <v>1</v>
       </c>
       <c r="D24" s="12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F24" s="12"/>
+        <v>57</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>58</v>
+      </c>
       <c r="G24" s="12">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I24" s="12">
         <v>0</v>
@@ -6194,39 +6247,39 @@
       <c r="J24" s="12">
         <v>0</v>
       </c>
-      <c r="K24" s="12"/>
+      <c r="K24" s="12" t="s">
+        <v>59</v>
+      </c>
       <c r="L24" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M24" s="12"/>
       <c r="N24" s="12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="12">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C25" s="12">
         <v>1</v>
       </c>
       <c r="D25" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F25" s="12"/>
       <c r="G25" s="12">
         <v>0</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I25" s="12">
         <v>0</v>
@@ -6234,35 +6287,33 @@
       <c r="J25" s="12">
         <v>0</v>
       </c>
-      <c r="K25" s="12" t="s">
-        <v>68</v>
-      </c>
+      <c r="K25" s="12"/>
       <c r="L25" s="12" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="M25" s="12"/>
       <c r="N25" s="12" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="12">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C26" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="12">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>511</v>
+        <v>66</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G26" s="12">
         <v>0</v>
@@ -6276,33 +6327,35 @@
       <c r="J26" s="12">
         <v>0</v>
       </c>
-      <c r="K26" s="12"/>
+      <c r="K26" s="12" t="s">
+        <v>68</v>
+      </c>
       <c r="L26" s="12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M26" s="12"/>
       <c r="N26" s="12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="12">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C27" s="12">
         <v>2</v>
       </c>
       <c r="D27" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>76</v>
+        <v>511</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G27" s="12">
         <v>0</v>
@@ -6318,31 +6371,31 @@
       </c>
       <c r="K27" s="12"/>
       <c r="L27" s="12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="M27" s="12"/>
       <c r="N27" s="12" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="12">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C28" s="12">
         <v>2</v>
       </c>
       <c r="D28" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G28" s="12">
         <v>0</v>
@@ -6356,35 +6409,33 @@
       <c r="J28" s="12">
         <v>0</v>
       </c>
-      <c r="K28" s="12" t="s">
-        <v>83</v>
-      </c>
+      <c r="K28" s="12"/>
       <c r="L28" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="M28" s="12"/>
       <c r="N28" s="12" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="12">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C29" s="12">
         <v>2</v>
       </c>
       <c r="D29" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G29" s="12">
         <v>0</v>
@@ -6393,40 +6444,40 @@
         <v>17</v>
       </c>
       <c r="I29" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="M29" s="12"/>
       <c r="N29" s="12" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="12">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C30" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" s="12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G30" s="12">
         <v>0</v>
@@ -6435,40 +6486,40 @@
         <v>17</v>
       </c>
       <c r="I30" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M30" s="12"/>
       <c r="N30" s="12" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="12">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C31" s="12">
         <v>3</v>
       </c>
       <c r="D31" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G31" s="12">
         <v>0</v>
@@ -6483,34 +6534,34 @@
         <v>0</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M31" s="12"/>
       <c r="N31" s="12" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="12">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C32" s="12">
         <v>3</v>
       </c>
       <c r="D32" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G32" s="12">
         <v>0</v>
@@ -6525,34 +6576,34 @@
         <v>0</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M32" s="12"/>
       <c r="N32" s="12" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="12">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C33" s="12">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D33" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>605</v>
+        <v>103</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G33" s="12">
         <v>0</v>
@@ -6567,38 +6618,40 @@
         <v>0</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>575</v>
+        <v>105</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>606</v>
+        <v>103</v>
       </c>
       <c r="M33" s="12"/>
       <c r="N33" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="12">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>636</v>
+        <v>107</v>
       </c>
       <c r="C34" s="12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D34" s="12">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="F34" s="12"/>
+        <v>605</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="G34" s="12">
         <v>0</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I34" s="12">
         <v>0</v>
@@ -6606,39 +6659,39 @@
       <c r="J34" s="12">
         <v>0</v>
       </c>
-      <c r="K34" s="12"/>
+      <c r="K34" s="12" t="s">
+        <v>575</v>
+      </c>
       <c r="L34" s="12" t="s">
-        <v>111</v>
+        <v>606</v>
       </c>
       <c r="M34" s="12"/>
       <c r="N34" s="12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="12">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C35" s="12">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="D35" s="12">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>612</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="F35" s="12"/>
       <c r="G35" s="12">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I35" s="12">
         <v>0</v>
@@ -6646,35 +6699,33 @@
       <c r="J35" s="12">
         <v>0</v>
       </c>
-      <c r="K35" s="12" t="s">
-        <v>114</v>
-      </c>
+      <c r="K35" s="12"/>
       <c r="L35" s="12" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="M35" s="12"/>
       <c r="N35" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="12">
-        <v>500</v>
+        <v>119</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>676</v>
+        <v>637</v>
       </c>
       <c r="C36" s="12">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D36" s="12">
         <v>1</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>118</v>
+        <v>612</v>
       </c>
       <c r="G36" s="12">
         <v>0</v>
@@ -6689,34 +6740,34 @@
         <v>0</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>711</v>
+        <v>114</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M36" s="12"/>
       <c r="N36" s="12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="12">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>121</v>
+        <v>676</v>
       </c>
       <c r="C37" s="12">
         <v>108</v>
       </c>
       <c r="D37" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G37" s="12">
         <v>0</v>
@@ -6731,40 +6782,40 @@
         <v>0</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="M37" s="12"/>
       <c r="N37" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="12">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>528</v>
+        <v>121</v>
       </c>
       <c r="C38" s="12">
         <v>108</v>
       </c>
       <c r="D38" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>760</v>
+        <v>122</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>529</v>
+        <v>123</v>
       </c>
       <c r="G38" s="12">
         <v>0</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>530</v>
+        <v>17</v>
       </c>
       <c r="I38" s="12">
         <v>0</v>
@@ -6773,36 +6824,40 @@
         <v>0</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>534</v>
+        <v>710</v>
       </c>
       <c r="L38" s="12" t="s">
-        <v>531</v>
+        <v>122</v>
       </c>
       <c r="M38" s="12"/>
       <c r="N38" s="12" t="s">
-        <v>626</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="12">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>784</v>
+        <v>528</v>
       </c>
       <c r="C39" s="12">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D39" s="12">
-        <v>1</v>
-      </c>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>760</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>529</v>
+      </c>
       <c r="G39" s="12">
         <v>0</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>785</v>
+        <v>530</v>
       </c>
       <c r="I39" s="12">
         <v>0</v>
@@ -6811,18 +6866,22 @@
         <v>0</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>786</v>
-      </c>
-      <c r="L39" s="12"/>
+        <v>534</v>
+      </c>
+      <c r="L39" s="12" t="s">
+        <v>531</v>
+      </c>
       <c r="M39" s="12"/>
-      <c r="N39" s="12"/>
+      <c r="N39" s="12" t="s">
+        <v>626</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="12">
-        <v>1001</v>
+        <v>503</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>125</v>
+        <v>784</v>
       </c>
       <c r="C40" s="12">
         <v>100</v>
@@ -6836,7 +6895,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>126</v>
+        <v>785</v>
       </c>
       <c r="I40" s="12">
         <v>0</v>
@@ -6845,7 +6904,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>127</v>
+        <v>786</v>
       </c>
       <c r="L40" s="12"/>
       <c r="M40" s="12"/>
@@ -6853,16 +6912,16 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="12">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C41" s="12">
         <v>100</v>
       </c>
       <c r="D41" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
@@ -6879,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L41" s="12"/>
       <c r="M41" s="12"/>
@@ -6887,16 +6946,16 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="12">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C42" s="12">
         <v>100</v>
       </c>
       <c r="D42" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
@@ -6913,7 +6972,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L42" s="12"/>
       <c r="M42" s="12"/>
@@ -6921,16 +6980,16 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="12">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C43" s="12">
         <v>100</v>
       </c>
       <c r="D43" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="12"/>
@@ -6947,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L43" s="12"/>
       <c r="M43" s="12"/>
@@ -6955,16 +7014,16 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="12">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C44" s="12">
         <v>100</v>
       </c>
       <c r="D44" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="12"/>
@@ -6981,26 +7040,24 @@
         <v>0</v>
       </c>
       <c r="K44" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="L44" s="12" t="s">
-        <v>136</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="L44" s="12"/>
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="12">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C45" s="12">
         <v>100</v>
       </c>
       <c r="D45" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="12"/>
@@ -7017,7 +7074,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="12" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L45" s="12" t="s">
         <v>136</v>
@@ -7027,16 +7084,16 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="12">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C46" s="12">
         <v>100</v>
       </c>
       <c r="D46" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="12"/>
@@ -7053,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L46" s="12" t="s">
         <v>136</v>
@@ -7063,16 +7120,16 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="12">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C47" s="12">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D47" s="12">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="12"/>
@@ -7089,7 +7146,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L47" s="12" t="s">
         <v>136</v>
@@ -7099,16 +7156,16 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="12">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C48" s="12">
         <v>101</v>
       </c>
       <c r="D48" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
@@ -7125,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L48" s="12" t="s">
         <v>136</v>
@@ -7135,16 +7192,16 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="12">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C49" s="12">
         <v>101</v>
       </c>
       <c r="D49" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="12"/>
@@ -7161,7 +7218,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L49" s="12" t="s">
         <v>136</v>
@@ -7171,16 +7228,16 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="12">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C50" s="12">
         <v>101</v>
       </c>
       <c r="D50" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="12"/>
@@ -7197,7 +7254,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L50" s="12" t="s">
         <v>136</v>
@@ -7207,16 +7264,16 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="12">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C51" s="12">
         <v>101</v>
       </c>
       <c r="D51" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="12"/>
@@ -7233,7 +7290,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L51" s="12" t="s">
         <v>136</v>
@@ -7243,16 +7300,16 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="12">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C52" s="12">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D52" s="12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="12"/>
@@ -7269,7 +7326,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L52" s="12" t="s">
         <v>136</v>
@@ -7279,16 +7336,16 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="12">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C53" s="12">
         <v>102</v>
       </c>
       <c r="D53" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
@@ -7305,7 +7362,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L53" s="12" t="s">
         <v>136</v>
@@ -7315,16 +7372,16 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="12">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C54" s="12">
         <v>102</v>
       </c>
       <c r="D54" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12"/>
@@ -7341,7 +7398,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L54" s="12" t="s">
         <v>136</v>
@@ -7351,16 +7408,16 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="12">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C55" s="12">
         <v>102</v>
       </c>
       <c r="D55" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="12"/>
@@ -7377,7 +7434,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L55" s="12" t="s">
         <v>136</v>
@@ -7387,16 +7444,16 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="12">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C56" s="12">
         <v>102</v>
       </c>
       <c r="D56" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12"/>
@@ -7413,24 +7470,26 @@
         <v>0</v>
       </c>
       <c r="K56" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="L56" s="12"/>
+        <v>158</v>
+      </c>
+      <c r="L56" s="12" t="s">
+        <v>136</v>
+      </c>
       <c r="M56" s="12"/>
       <c r="N56" s="12"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="12">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C57" s="12">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D57" s="12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12"/>
@@ -7447,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L57" s="12"/>
       <c r="M57" s="12"/>
@@ -7455,16 +7514,16 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="12">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C58" s="12">
         <v>103</v>
       </c>
       <c r="D58" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="12"/>
@@ -7481,7 +7540,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L58" s="12"/>
       <c r="M58" s="12"/>
@@ -7489,16 +7548,16 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="12">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C59" s="12">
         <v>103</v>
       </c>
       <c r="D59" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="12"/>
@@ -7515,7 +7574,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L59" s="12"/>
       <c r="M59" s="12"/>
@@ -7523,16 +7582,16 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="12">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C60" s="12">
         <v>103</v>
       </c>
       <c r="D60" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="12"/>
@@ -7549,7 +7608,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L60" s="12"/>
       <c r="M60" s="12"/>
@@ -7557,16 +7616,16 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="12">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C61" s="12">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="12"/>
@@ -7583,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="12" t="s">
-        <v>44</v>
+        <v>168</v>
       </c>
       <c r="L61" s="12"/>
       <c r="M61" s="12"/>
@@ -7591,16 +7650,16 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="12">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C62" s="12">
         <v>104</v>
       </c>
       <c r="D62" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="12"/>
@@ -7617,7 +7676,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="12" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="L62" s="12"/>
       <c r="M62" s="12"/>
@@ -7625,16 +7684,16 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="12">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C63" s="12">
         <v>104</v>
       </c>
       <c r="D63" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="12"/>
@@ -7651,7 +7710,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L63" s="12"/>
       <c r="M63" s="12"/>
@@ -7659,16 +7718,16 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="12">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C64" s="12">
         <v>104</v>
       </c>
       <c r="D64" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="12"/>
@@ -7685,7 +7744,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L64" s="12"/>
       <c r="M64" s="12"/>
@@ -7693,16 +7752,16 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="12">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C65" s="12">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D65" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="12"/>
@@ -7719,7 +7778,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L65" s="12"/>
       <c r="M65" s="12"/>
@@ -7727,16 +7786,16 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="12">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C66" s="12">
         <v>105</v>
       </c>
       <c r="D66" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12"/>
@@ -7753,7 +7812,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="L66" s="12"/>
       <c r="M66" s="12"/>
@@ -7761,16 +7820,16 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="12">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C67" s="12">
         <v>105</v>
       </c>
       <c r="D67" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
@@ -7787,7 +7846,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="L67" s="12"/>
       <c r="M67" s="12"/>
@@ -7795,16 +7854,16 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="12">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C68" s="12">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D68" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12"/>
@@ -7821,7 +7880,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L68" s="12"/>
       <c r="M68" s="12"/>
@@ -7829,16 +7888,16 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="12">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C69" s="12">
         <v>106</v>
       </c>
       <c r="D69" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="12"/>
@@ -7855,7 +7914,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L69" s="12"/>
       <c r="M69" s="12"/>
@@ -7863,16 +7922,16 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="12">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C70" s="12">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D70" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" s="12"/>
       <c r="F70" s="12"/>
@@ -7889,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="L70" s="12"/>
       <c r="M70" s="12"/>
@@ -7897,20 +7956,18 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="12">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C71" s="12">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D71" s="12">
         <v>1</v>
       </c>
-      <c r="E71" s="12" t="s">
-        <v>136</v>
-      </c>
+      <c r="E71" s="12"/>
       <c r="F71" s="12"/>
       <c r="G71" s="12">
         <v>0</v>
@@ -7925,26 +7982,24 @@
         <v>0</v>
       </c>
       <c r="K71" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="L71" s="12" t="s">
-        <v>136</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="L71" s="12"/>
       <c r="M71" s="12"/>
       <c r="N71" s="12"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="12">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C72" s="12">
         <v>110</v>
       </c>
       <c r="D72" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>136</v>
@@ -7963,24 +8018,26 @@
         <v>0</v>
       </c>
       <c r="K72" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="L72" s="12"/>
+        <v>189</v>
+      </c>
+      <c r="L72" s="12" t="s">
+        <v>136</v>
+      </c>
       <c r="M72" s="12"/>
       <c r="N72" s="12"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="12">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C73" s="12">
         <v>110</v>
       </c>
       <c r="D73" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73" s="12" t="s">
         <v>136</v>
@@ -7999,7 +8056,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L73" s="12"/>
       <c r="M73" s="12"/>
@@ -8007,16 +8064,16 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="12">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C74" s="12">
         <v>110</v>
       </c>
       <c r="D74" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>136</v>
@@ -8035,7 +8092,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L74" s="12"/>
       <c r="M74" s="12"/>
@@ -8043,16 +8100,16 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="12">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C75" s="12">
         <v>110</v>
       </c>
       <c r="D75" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E75" s="12" t="s">
         <v>136</v>
@@ -8071,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L75" s="12"/>
       <c r="M75" s="12"/>
@@ -8079,16 +8136,16 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="12">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C76" s="12">
         <v>110</v>
       </c>
       <c r="D76" s="12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>136</v>
@@ -8107,7 +8164,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L76" s="12"/>
       <c r="M76" s="12"/>
@@ -8115,16 +8172,16 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="12">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C77" s="12">
         <v>110</v>
       </c>
       <c r="D77" s="12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E77" s="12" t="s">
         <v>136</v>
@@ -8143,7 +8200,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L77" s="12"/>
       <c r="M77" s="12"/>
@@ -8151,92 +8208,92 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="12">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C78" s="12">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="D78" s="12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>204</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="F78" s="12"/>
       <c r="G78" s="12">
         <v>0</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="I78" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" s="12">
         <v>0</v>
       </c>
       <c r="K78" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="L78" s="12" t="s">
-        <v>63</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="L78" s="12"/>
       <c r="M78" s="12"/>
       <c r="N78" s="12"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="12">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C79" s="12">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="D79" s="12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="F79" s="12"/>
+        <v>203</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>204</v>
+      </c>
       <c r="G79" s="12">
         <v>0</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="I79" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="12">
         <v>0</v>
       </c>
       <c r="K79" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="L79" s="12"/>
+        <v>205</v>
+      </c>
+      <c r="L79" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="M79" s="12"/>
       <c r="N79" s="12"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="12">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C80" s="12">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="D80" s="12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>136</v>
@@ -8255,7 +8312,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L80" s="12"/>
       <c r="M80" s="12"/>
@@ -8263,16 +8320,16 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="12">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C81" s="12">
         <v>500</v>
       </c>
       <c r="D81" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="12" t="s">
         <v>136</v>
@@ -8291,7 +8348,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L81" s="12"/>
       <c r="M81" s="12"/>
@@ -8299,16 +8356,16 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="12">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C82" s="12">
         <v>500</v>
       </c>
       <c r="D82" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" s="12" t="s">
         <v>136</v>
@@ -8327,7 +8384,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L82" s="12"/>
       <c r="M82" s="12"/>
@@ -8335,16 +8392,16 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="12">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C83" s="12">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D83" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83" s="12" t="s">
         <v>136</v>
@@ -8363,7 +8420,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L83" s="12"/>
       <c r="M83" s="12"/>
@@ -8371,10 +8428,10 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="12">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C84" s="12">
         <v>501</v>
@@ -8399,7 +8456,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L84" s="12"/>
       <c r="M84" s="12"/>
@@ -8407,10 +8464,10 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="12">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C85" s="12">
         <v>501</v>
@@ -8435,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L85" s="12"/>
       <c r="M85" s="12"/>
@@ -8443,100 +8500,102 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="12">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>701</v>
+        <v>218</v>
       </c>
       <c r="C86" s="12">
-        <v>118</v>
+        <v>501</v>
       </c>
       <c r="D86" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>602</v>
-      </c>
-      <c r="F86" s="12" t="s">
-        <v>635</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="F86" s="12"/>
       <c r="G86" s="12">
         <v>0</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>530</v>
+        <v>126</v>
       </c>
       <c r="I86" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" s="12">
         <v>0</v>
       </c>
       <c r="K86" s="12" t="s">
-        <v>603</v>
-      </c>
-      <c r="L86" s="12" t="s">
-        <v>63</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="L86" s="12"/>
       <c r="M86" s="12"/>
       <c r="N86" s="12"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="12">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>638</v>
+        <v>701</v>
       </c>
       <c r="C87" s="12">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D87" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="F87" s="12"/>
+        <v>602</v>
+      </c>
+      <c r="F87" s="12" t="s">
+        <v>635</v>
+      </c>
       <c r="G87" s="12">
         <v>0</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>126</v>
+        <v>530</v>
       </c>
       <c r="I87" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" s="12">
         <v>0</v>
       </c>
       <c r="K87" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="L87" s="12"/>
+        <v>603</v>
+      </c>
+      <c r="L87" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="M87" s="12"/>
       <c r="N87" s="12"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="12">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>700</v>
+        <v>638</v>
       </c>
       <c r="C88" s="12">
         <v>119</v>
       </c>
-      <c r="D88" s="12"/>
+      <c r="D88" s="12">
+        <v>3</v>
+      </c>
       <c r="E88" s="12" t="s">
-        <v>526</v>
+        <v>136</v>
       </c>
       <c r="F88" s="12"/>
       <c r="G88" s="12">
         <v>0</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>525</v>
+        <v>126</v>
       </c>
       <c r="I88" s="12">
         <v>0</v>
@@ -8545,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="12" t="s">
-        <v>702</v>
+        <v>220</v>
       </c>
       <c r="L88" s="12"/>
       <c r="M88" s="12"/>
@@ -8553,26 +8612,24 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="12">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>639</v>
+        <v>700</v>
       </c>
       <c r="C89" s="12">
         <v>119</v>
       </c>
-      <c r="D89" s="12">
-        <v>4</v>
-      </c>
+      <c r="D89" s="12"/>
       <c r="E89" s="12" t="s">
-        <v>136</v>
+        <v>526</v>
       </c>
       <c r="F89" s="12"/>
       <c r="G89" s="12">
         <v>0</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>126</v>
+        <v>525</v>
       </c>
       <c r="I89" s="12">
         <v>0</v>
@@ -8581,7 +8638,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="12" t="s">
-        <v>221</v>
+        <v>702</v>
       </c>
       <c r="L89" s="12"/>
       <c r="M89" s="12"/>
@@ -8589,16 +8646,16 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="12">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>222</v>
+        <v>639</v>
       </c>
       <c r="C90" s="12">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D90" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" s="12" t="s">
         <v>136</v>
@@ -8617,7 +8674,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L90" s="12"/>
       <c r="M90" s="12"/>
@@ -8625,16 +8682,16 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="12">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C91" s="12">
         <v>109</v>
       </c>
       <c r="D91" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" s="12" t="s">
         <v>136</v>
@@ -8653,7 +8710,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L91" s="12"/>
       <c r="M91" s="12"/>
@@ -8661,16 +8718,16 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="12">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C92" s="12">
         <v>109</v>
       </c>
       <c r="D92" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E92" s="12" t="s">
         <v>136</v>
@@ -8689,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L92" s="12"/>
       <c r="M92" s="12"/>
@@ -8697,16 +8754,16 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="12">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C93" s="12">
         <v>109</v>
       </c>
       <c r="D93" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E93" s="12" t="s">
         <v>136</v>
@@ -8725,7 +8782,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L93" s="12"/>
       <c r="M93" s="12"/>
@@ -8733,16 +8790,16 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="12">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C94" s="12">
         <v>109</v>
       </c>
       <c r="D94" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E94" s="12" t="s">
         <v>136</v>
@@ -8761,7 +8818,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L94" s="12"/>
       <c r="M94" s="12"/>
@@ -8769,37 +8826,35 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="12">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C95" s="12">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="D95" s="12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="F95" s="12" t="s">
-        <v>234</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="F95" s="12"/>
       <c r="G95" s="12">
         <v>0</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="I95" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" s="12">
         <v>0</v>
       </c>
       <c r="K95" s="12" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L95" s="12"/>
       <c r="M95" s="12"/>
@@ -8807,35 +8862,37 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="12">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C96" s="12">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="D96" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="F96" s="12"/>
+        <v>233</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>234</v>
+      </c>
       <c r="G96" s="12">
         <v>0</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="I96" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" s="12">
         <v>0</v>
       </c>
       <c r="K96" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L96" s="12"/>
       <c r="M96" s="12"/>
@@ -8843,16 +8900,16 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="12">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C97" s="12">
         <v>115</v>
       </c>
       <c r="D97" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" s="12" t="s">
         <v>136</v>
@@ -8871,7 +8928,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L97" s="12"/>
       <c r="M97" s="12"/>
@@ -8879,10 +8936,10 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="12">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C98" s="12">
         <v>115</v>
@@ -8907,7 +8964,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L98" s="12"/>
       <c r="M98" s="12"/>
@@ -8915,10 +8972,10 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="12">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C99" s="12">
         <v>115</v>
@@ -8943,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L99" s="12"/>
       <c r="M99" s="12"/>
@@ -8951,10 +9008,10 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="12">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C100" s="12">
         <v>115</v>
@@ -8979,7 +9036,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L100" s="12"/>
       <c r="M100" s="12"/>
@@ -8987,18 +9044,20 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="12">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C101" s="12">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D101" s="12">
-        <v>4</v>
-      </c>
-      <c r="E101" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>136</v>
+      </c>
       <c r="F101" s="12"/>
       <c r="G101" s="12">
         <v>0</v>
@@ -9013,7 +9072,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L101" s="12"/>
       <c r="M101" s="12"/>
@@ -9021,13 +9080,13 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="12">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C102" s="12">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D102" s="12">
         <v>4</v>
@@ -9047,7 +9106,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L102" s="12"/>
       <c r="M102" s="12"/>
@@ -9055,28 +9114,24 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="12">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C103" s="12">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="D103" s="12">
-        <v>17</v>
-      </c>
-      <c r="E103" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="F103" s="12" t="s">
-        <v>252</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E103" s="12"/>
+      <c r="F103" s="12"/>
       <c r="G103" s="12">
         <v>0</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="I103" s="12">
         <v>0</v>
@@ -9085,38 +9140,36 @@
         <v>0</v>
       </c>
       <c r="K103" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="L103" s="12" t="s">
-        <v>254</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="L103" s="12"/>
       <c r="M103" s="12"/>
-      <c r="N103" s="12" t="s">
-        <v>255</v>
-      </c>
+      <c r="N103" s="12"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="12">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C104" s="12">
-        <v>1072</v>
+        <v>3</v>
       </c>
       <c r="D104" s="12">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="F104" s="12"/>
+        <v>251</v>
+      </c>
+      <c r="F104" s="12" t="s">
+        <v>252</v>
+      </c>
       <c r="G104" s="12">
         <v>0</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="I104" s="12">
         <v>0</v>
@@ -9125,24 +9178,28 @@
         <v>0</v>
       </c>
       <c r="K104" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="L104" s="12"/>
+        <v>253</v>
+      </c>
+      <c r="L104" s="12" t="s">
+        <v>254</v>
+      </c>
       <c r="M104" s="12"/>
-      <c r="N104" s="12"/>
+      <c r="N104" s="12" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="12">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C105" s="12">
         <v>1072</v>
       </c>
       <c r="D105" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" s="12" t="s">
         <v>136</v>
@@ -9161,7 +9218,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L105" s="12"/>
       <c r="M105" s="12"/>
@@ -9169,16 +9226,16 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="12">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C106" s="12">
         <v>1072</v>
       </c>
       <c r="D106" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106" s="12" t="s">
         <v>136</v>
@@ -9197,7 +9254,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L106" s="12"/>
       <c r="M106" s="12"/>
@@ -9205,16 +9262,16 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="12">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C107" s="12">
         <v>1072</v>
       </c>
       <c r="D107" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E107" s="12" t="s">
         <v>136</v>
@@ -9233,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L107" s="12"/>
       <c r="M107" s="12"/>
@@ -9241,16 +9298,16 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="12">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C108" s="12">
         <v>1072</v>
       </c>
       <c r="D108" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E108" s="12" t="s">
         <v>136</v>
@@ -9269,7 +9326,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L108" s="12"/>
       <c r="M108" s="12"/>
@@ -9277,28 +9334,26 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="12">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C109" s="12">
-        <v>1</v>
+        <v>1072</v>
       </c>
       <c r="D109" s="12">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>691</v>
-      </c>
-      <c r="F109" s="12" t="s">
-        <v>267</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="F109" s="12"/>
       <c r="G109" s="12">
         <v>0</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="I109" s="12">
         <v>0</v>
@@ -9307,38 +9362,36 @@
         <v>0</v>
       </c>
       <c r="K109" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="L109" s="12" t="s">
-        <v>269</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="L109" s="12"/>
       <c r="M109" s="12"/>
-      <c r="N109" s="12" t="s">
-        <v>270</v>
-      </c>
+      <c r="N109" s="12"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="12">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="C110" s="12">
-        <v>1078</v>
+        <v>1</v>
       </c>
       <c r="D110" s="12">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="F110" s="12"/>
+        <v>691</v>
+      </c>
+      <c r="F110" s="12" t="s">
+        <v>267</v>
+      </c>
       <c r="G110" s="12">
         <v>0</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="I110" s="12">
         <v>0</v>
@@ -9347,24 +9400,28 @@
         <v>0</v>
       </c>
       <c r="K110" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="L110" s="12"/>
+        <v>268</v>
+      </c>
+      <c r="L110" s="12" t="s">
+        <v>269</v>
+      </c>
       <c r="M110" s="12"/>
-      <c r="N110" s="12"/>
+      <c r="N110" s="12" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="12">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C111" s="12">
         <v>1078</v>
       </c>
       <c r="D111" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" s="12" t="s">
         <v>136</v>
@@ -9383,7 +9440,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L111" s="12"/>
       <c r="M111" s="12"/>
@@ -9391,16 +9448,16 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="12">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C112" s="12">
         <v>1078</v>
       </c>
       <c r="D112" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E112" s="12" t="s">
         <v>136</v>
@@ -9419,7 +9476,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L112" s="12"/>
       <c r="M112" s="12"/>
@@ -9427,16 +9484,16 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="12">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C113" s="12">
         <v>1078</v>
       </c>
       <c r="D113" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E113" s="12" t="s">
         <v>136</v>
@@ -9455,7 +9512,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L113" s="12"/>
       <c r="M113" s="12"/>
@@ -9463,26 +9520,26 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="12">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>527</v>
+        <v>262</v>
       </c>
       <c r="C114" s="12">
         <v>1078</v>
       </c>
       <c r="D114" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>526</v>
+        <v>136</v>
       </c>
       <c r="F114" s="12"/>
       <c r="G114" s="12">
         <v>0</v>
       </c>
       <c r="H114" s="12" t="s">
-        <v>525</v>
+        <v>126</v>
       </c>
       <c r="I114" s="12">
         <v>0</v>
@@ -9491,7 +9548,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="12" t="s">
-        <v>524</v>
+        <v>274</v>
       </c>
       <c r="L114" s="12"/>
       <c r="M114" s="12"/>
@@ -9499,10 +9556,10 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="12">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>264</v>
+        <v>527</v>
       </c>
       <c r="C115" s="12">
         <v>1078</v>
@@ -9511,14 +9568,14 @@
         <v>5</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>136</v>
+        <v>526</v>
       </c>
       <c r="F115" s="12"/>
       <c r="G115" s="12">
         <v>0</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>126</v>
+        <v>525</v>
       </c>
       <c r="I115" s="12">
         <v>0</v>
@@ -9527,76 +9584,72 @@
         <v>0</v>
       </c>
       <c r="K115" s="12" t="s">
-        <v>275</v>
+        <v>524</v>
       </c>
       <c r="L115" s="12"/>
       <c r="M115" s="12"/>
       <c r="N115" s="12"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A116" s="14">
-        <v>1084</v>
-      </c>
-      <c r="B116" s="14" t="s">
-        <v>640</v>
-      </c>
-      <c r="C116" s="14">
-        <v>118</v>
-      </c>
-      <c r="D116" s="14">
-        <v>999</v>
-      </c>
-      <c r="E116" s="14" t="s">
-        <v>690</v>
-      </c>
-      <c r="F116" s="14" t="s">
-        <v>613</v>
-      </c>
-      <c r="G116" s="14">
-        <v>0</v>
-      </c>
-      <c r="H116" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I116" s="14">
-        <v>0</v>
-      </c>
-      <c r="J116" s="14">
-        <v>0</v>
-      </c>
-      <c r="K116" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="L116" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="M116" s="14"/>
-      <c r="N116" s="12" t="s">
-        <v>623</v>
-      </c>
+      <c r="A116" s="12">
+        <v>1083</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C116" s="12">
+        <v>1078</v>
+      </c>
+      <c r="D116" s="12">
+        <v>5</v>
+      </c>
+      <c r="E116" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12">
+        <v>0</v>
+      </c>
+      <c r="H116" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I116" s="12">
+        <v>0</v>
+      </c>
+      <c r="J116" s="12">
+        <v>0</v>
+      </c>
+      <c r="K116" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="L116" s="12"/>
+      <c r="M116" s="12"/>
+      <c r="N116" s="12"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="14">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B117" s="14" t="s">
-        <v>256</v>
+        <v>640</v>
       </c>
       <c r="C117" s="14">
-        <v>1084</v>
+        <v>118</v>
       </c>
       <c r="D117" s="14">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="E117" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="F117" s="14"/>
+        <v>690</v>
+      </c>
+      <c r="F117" s="14" t="s">
+        <v>613</v>
+      </c>
       <c r="G117" s="14">
         <v>0</v>
       </c>
       <c r="H117" s="14" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="I117" s="14">
         <v>0</v>
@@ -9605,24 +9658,28 @@
         <v>0</v>
       </c>
       <c r="K117" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="L117" s="14"/>
+        <v>276</v>
+      </c>
+      <c r="L117" s="14" t="s">
+        <v>33</v>
+      </c>
       <c r="M117" s="14"/>
-      <c r="N117" s="12"/>
+      <c r="N117" s="12" t="s">
+        <v>623</v>
+      </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="14">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B118" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C118" s="14">
         <v>1084</v>
       </c>
       <c r="D118" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" s="14" t="s">
         <v>136</v>
@@ -9641,7 +9698,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L118" s="14"/>
       <c r="M118" s="14"/>
@@ -9649,16 +9706,16 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="14">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B119" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C119" s="14">
         <v>1084</v>
       </c>
       <c r="D119" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E119" s="14" t="s">
         <v>136</v>
@@ -9677,7 +9734,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L119" s="14"/>
       <c r="M119" s="14"/>
@@ -9685,16 +9742,16 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="14">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C120" s="14">
         <v>1084</v>
       </c>
       <c r="D120" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E120" s="14" t="s">
         <v>136</v>
@@ -9713,7 +9770,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L120" s="14"/>
       <c r="M120" s="14"/>
@@ -9721,16 +9778,16 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="14">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B121" s="14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C121" s="14">
         <v>1084</v>
       </c>
       <c r="D121" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E121" s="14" t="s">
         <v>136</v>
@@ -9749,60 +9806,60 @@
         <v>0</v>
       </c>
       <c r="K121" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L121" s="14"/>
       <c r="M121" s="14"/>
       <c r="N121" s="12"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A122" s="12">
-        <v>1092</v>
-      </c>
-      <c r="B122" s="12" t="s">
-        <v>544</v>
-      </c>
-      <c r="C122" s="12">
-        <v>111</v>
-      </c>
-      <c r="D122" s="12">
-        <v>1</v>
-      </c>
-      <c r="E122" s="12"/>
-      <c r="F122" s="12"/>
-      <c r="G122" s="12">
-        <v>0</v>
-      </c>
-      <c r="H122" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="I122" s="12">
-        <v>0</v>
-      </c>
-      <c r="J122" s="12">
-        <v>0</v>
-      </c>
-      <c r="K122" s="12" t="s">
-        <v>545</v>
-      </c>
-      <c r="L122" s="12"/>
-      <c r="M122" s="12" t="s">
-        <v>550</v>
-      </c>
+      <c r="A122" s="14">
+        <v>1089</v>
+      </c>
+      <c r="B122" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C122" s="14">
+        <v>1084</v>
+      </c>
+      <c r="D122" s="14">
+        <v>5</v>
+      </c>
+      <c r="E122" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="F122" s="14"/>
+      <c r="G122" s="14">
+        <v>0</v>
+      </c>
+      <c r="H122" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="I122" s="14">
+        <v>0</v>
+      </c>
+      <c r="J122" s="14">
+        <v>0</v>
+      </c>
+      <c r="K122" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="L122" s="14"/>
+      <c r="M122" s="14"/>
       <c r="N122" s="12"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="12">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C123" s="12">
         <v>111</v>
       </c>
       <c r="D123" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" s="12"/>
       <c r="F123" s="12"/>
@@ -9819,7 +9876,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="12" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L123" s="12"/>
       <c r="M123" s="12" t="s">
@@ -9829,13 +9886,13 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="12">
-        <v>1102</v>
+        <v>1091</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="C124" s="12">
-        <v>502</v>
+        <v>111</v>
       </c>
       <c r="D124" s="12">
         <v>2</v>
@@ -9855,26 +9912,26 @@
         <v>0</v>
       </c>
       <c r="K124" s="12" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="L124" s="12"/>
       <c r="M124" s="12" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N124" s="12"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="12">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C125" s="12">
         <v>502</v>
       </c>
       <c r="D125" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E125" s="12"/>
       <c r="F125" s="12"/>
@@ -9891,102 +9948,104 @@
         <v>0</v>
       </c>
       <c r="K125" s="12" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L125" s="12"/>
       <c r="M125" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="N125" s="12"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A126" s="12">
+        <v>1103</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="C126" s="12">
+        <v>502</v>
+      </c>
+      <c r="D126" s="12">
+        <v>3</v>
+      </c>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12">
+        <v>0</v>
+      </c>
+      <c r="H126" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="I126" s="12">
+        <v>0</v>
+      </c>
+      <c r="J126" s="12">
+        <v>0</v>
+      </c>
+      <c r="K126" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="L126" s="12"/>
+      <c r="M126" s="12" t="s">
         <v>548</v>
       </c>
-      <c r="N125" s="12"/>
-    </row>
-    <row r="126" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="15">
+      <c r="N126" s="12"/>
+    </row>
+    <row r="127" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="15">
         <v>1104</v>
       </c>
-      <c r="B126" s="15" t="s">
+      <c r="B127" s="15" t="s">
         <v>564</v>
       </c>
-      <c r="C126" s="15">
+      <c r="C127" s="15">
         <v>9</v>
       </c>
-      <c r="D126" s="15">
-        <v>1</v>
-      </c>
-      <c r="E126" s="15" t="s">
+      <c r="D127" s="15">
+        <v>1</v>
+      </c>
+      <c r="E127" s="15" t="s">
         <v>567</v>
       </c>
-      <c r="F126" s="15" t="s">
+      <c r="F127" s="15" t="s">
         <v>568</v>
       </c>
-      <c r="G126" s="15">
-        <v>0</v>
-      </c>
-      <c r="H126" s="15" t="s">
+      <c r="G127" s="15">
+        <v>0</v>
+      </c>
+      <c r="H127" s="15" t="s">
         <v>530</v>
       </c>
-      <c r="I126" s="15">
-        <v>0</v>
-      </c>
-      <c r="J126" s="15">
-        <v>0</v>
-      </c>
-      <c r="K126" s="15" t="s">
+      <c r="I127" s="15">
+        <v>0</v>
+      </c>
+      <c r="J127" s="15">
+        <v>0</v>
+      </c>
+      <c r="K127" s="15" t="s">
         <v>574</v>
       </c>
-      <c r="L126" s="15" t="s">
+      <c r="L127" s="15" t="s">
         <v>576</v>
       </c>
-      <c r="M126" s="15"/>
-      <c r="N126" s="12" t="s">
+      <c r="M127" s="15"/>
+      <c r="N127" s="12" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A127" s="15">
-        <v>1105</v>
-      </c>
-      <c r="B127" s="15" t="s">
-        <v>569</v>
-      </c>
-      <c r="C127" s="15">
-        <v>1104</v>
-      </c>
-      <c r="D127" s="15">
-        <v>2</v>
-      </c>
-      <c r="E127" s="15"/>
-      <c r="F127" s="15"/>
-      <c r="G127" s="15">
-        <v>0</v>
-      </c>
-      <c r="H127" s="15" t="s">
-        <v>525</v>
-      </c>
-      <c r="I127" s="15">
-        <v>0</v>
-      </c>
-      <c r="J127" s="15">
-        <v>0</v>
-      </c>
-      <c r="K127" s="15" t="s">
-        <v>571</v>
-      </c>
-      <c r="L127" s="15"/>
-      <c r="M127" s="15"/>
-      <c r="N127" s="12"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="15">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C128" s="15">
         <v>1104</v>
       </c>
       <c r="D128" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E128" s="15"/>
       <c r="F128" s="15"/>
@@ -10003,7 +10062,7 @@
         <v>0</v>
       </c>
       <c r="K128" s="15" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="L128" s="15"/>
       <c r="M128" s="15"/>
@@ -10011,16 +10070,16 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="15">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="C129" s="15">
         <v>1104</v>
       </c>
       <c r="D129" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E129" s="15"/>
       <c r="F129" s="15"/>
@@ -10037,74 +10096,70 @@
         <v>0</v>
       </c>
       <c r="K129" s="15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L129" s="15"/>
       <c r="M129" s="15"/>
       <c r="N129" s="12"/>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A130" s="16">
-        <v>1108</v>
-      </c>
-      <c r="B130" s="16" t="s">
-        <v>585</v>
-      </c>
-      <c r="C130" s="16">
-        <v>108</v>
-      </c>
-      <c r="D130" s="16">
-        <v>1</v>
-      </c>
-      <c r="E130" s="16" t="s">
-        <v>580</v>
-      </c>
-      <c r="F130" s="16" t="s">
-        <v>581</v>
-      </c>
-      <c r="G130" s="16">
-        <v>0</v>
-      </c>
-      <c r="H130" s="16" t="s">
-        <v>530</v>
-      </c>
-      <c r="I130" s="16">
-        <v>0</v>
-      </c>
-      <c r="J130" s="16">
-        <v>0</v>
-      </c>
-      <c r="K130" s="16" t="s">
-        <v>582</v>
-      </c>
-      <c r="L130" s="16" t="s">
-        <v>577</v>
-      </c>
-      <c r="M130" s="16"/>
-      <c r="N130" s="12" t="s">
-        <v>627</v>
-      </c>
+      <c r="A130" s="15">
+        <v>1107</v>
+      </c>
+      <c r="B130" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="C130" s="15">
+        <v>1104</v>
+      </c>
+      <c r="D130" s="15">
+        <v>4</v>
+      </c>
+      <c r="E130" s="15"/>
+      <c r="F130" s="15"/>
+      <c r="G130" s="15">
+        <v>0</v>
+      </c>
+      <c r="H130" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="I130" s="15">
+        <v>0</v>
+      </c>
+      <c r="J130" s="15">
+        <v>0</v>
+      </c>
+      <c r="K130" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="L130" s="15"/>
+      <c r="M130" s="15"/>
+      <c r="N130" s="12"/>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="16">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B131" s="16" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="C131" s="16">
-        <v>1108</v>
+        <v>108</v>
       </c>
       <c r="D131" s="16">
-        <v>2</v>
-      </c>
-      <c r="E131" s="16"/>
-      <c r="F131" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="E131" s="16" t="s">
+        <v>580</v>
+      </c>
+      <c r="F131" s="16" t="s">
+        <v>581</v>
+      </c>
       <c r="G131" s="16">
         <v>0</v>
       </c>
       <c r="H131" s="16" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="I131" s="16">
         <v>0</v>
@@ -10113,24 +10168,28 @@
         <v>0</v>
       </c>
       <c r="K131" s="16" t="s">
-        <v>583</v>
-      </c>
-      <c r="L131" s="16"/>
+        <v>582</v>
+      </c>
+      <c r="L131" s="16" t="s">
+        <v>577</v>
+      </c>
       <c r="M131" s="16"/>
-      <c r="N131" s="12"/>
+      <c r="N131" s="12" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="16">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B132" s="16" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C132" s="16">
         <v>1108</v>
       </c>
       <c r="D132" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E132" s="16"/>
       <c r="F132" s="16"/>
@@ -10147,76 +10206,70 @@
         <v>0</v>
       </c>
       <c r="K132" s="16" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L132" s="16"/>
       <c r="M132" s="16"/>
       <c r="N132" s="12"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A133" s="14">
-        <v>1111</v>
-      </c>
-      <c r="B133" s="14" t="s">
-        <v>594</v>
-      </c>
-      <c r="C133" s="14">
-        <v>9</v>
-      </c>
-      <c r="D133" s="14">
-        <v>1</v>
-      </c>
-      <c r="E133" s="14" t="s">
-        <v>595</v>
-      </c>
-      <c r="F133" s="14" t="s">
-        <v>596</v>
-      </c>
-      <c r="G133" s="14">
-        <v>0</v>
-      </c>
-      <c r="H133" s="14" t="s">
-        <v>530</v>
-      </c>
-      <c r="I133" s="14">
-        <v>0</v>
-      </c>
-      <c r="J133" s="14">
-        <v>0</v>
-      </c>
-      <c r="K133" s="14" t="s">
-        <v>597</v>
-      </c>
-      <c r="L133" s="14" t="s">
-        <v>595</v>
-      </c>
-      <c r="M133" s="14" t="s">
-        <v>594</v>
-      </c>
-      <c r="N133" s="14" t="s">
-        <v>629</v>
-      </c>
+      <c r="A133" s="16">
+        <v>1110</v>
+      </c>
+      <c r="B133" s="16" t="s">
+        <v>579</v>
+      </c>
+      <c r="C133" s="16">
+        <v>1108</v>
+      </c>
+      <c r="D133" s="16">
+        <v>3</v>
+      </c>
+      <c r="E133" s="16"/>
+      <c r="F133" s="16"/>
+      <c r="G133" s="16">
+        <v>0</v>
+      </c>
+      <c r="H133" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="I133" s="16">
+        <v>0</v>
+      </c>
+      <c r="J133" s="16">
+        <v>0</v>
+      </c>
+      <c r="K133" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="L133" s="16"/>
+      <c r="M133" s="16"/>
+      <c r="N133" s="12"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="14">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B134" s="14" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C134" s="14">
-        <v>1111</v>
+        <v>9</v>
       </c>
       <c r="D134" s="14">
-        <v>2</v>
-      </c>
-      <c r="E134" s="14"/>
-      <c r="F134" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="E134" s="14" t="s">
+        <v>595</v>
+      </c>
+      <c r="F134" s="14" t="s">
+        <v>596</v>
+      </c>
       <c r="G134" s="14">
         <v>0</v>
       </c>
       <c r="H134" s="14" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="I134" s="14">
         <v>0</v>
@@ -10225,24 +10278,30 @@
         <v>0</v>
       </c>
       <c r="K134" s="14" t="s">
-        <v>598</v>
-      </c>
-      <c r="L134" s="14"/>
-      <c r="M134" s="14"/>
-      <c r="N134" s="12"/>
+        <v>597</v>
+      </c>
+      <c r="L134" s="14" t="s">
+        <v>595</v>
+      </c>
+      <c r="M134" s="14" t="s">
+        <v>594</v>
+      </c>
+      <c r="N134" s="14" t="s">
+        <v>629</v>
+      </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="14">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B135" s="14" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C135" s="14">
         <v>1111</v>
       </c>
       <c r="D135" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E135" s="14"/>
       <c r="F135" s="14"/>
@@ -10259,74 +10318,70 @@
         <v>0</v>
       </c>
       <c r="K135" s="14" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="L135" s="14"/>
       <c r="M135" s="14"/>
       <c r="N135" s="12"/>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A136" s="17">
-        <v>1114</v>
-      </c>
-      <c r="B136" s="17" t="s">
-        <v>618</v>
-      </c>
-      <c r="C136" s="17">
-        <v>2</v>
-      </c>
-      <c r="D136" s="17">
-        <v>1</v>
-      </c>
-      <c r="E136" s="17" t="s">
-        <v>689</v>
-      </c>
-      <c r="F136" s="17" t="s">
-        <v>614</v>
-      </c>
-      <c r="G136" s="17">
-        <v>0</v>
-      </c>
-      <c r="H136" s="17" t="s">
-        <v>530</v>
-      </c>
-      <c r="I136" s="17">
-        <v>0</v>
-      </c>
-      <c r="J136" s="17">
-        <v>0</v>
-      </c>
-      <c r="K136" s="17" t="s">
-        <v>615</v>
-      </c>
-      <c r="L136" s="17" t="s">
-        <v>531</v>
-      </c>
-      <c r="M136" s="17"/>
-      <c r="N136" s="12" t="s">
-        <v>625</v>
-      </c>
+      <c r="A136" s="14">
+        <v>1113</v>
+      </c>
+      <c r="B136" s="14" t="s">
+        <v>601</v>
+      </c>
+      <c r="C136" s="14">
+        <v>1111</v>
+      </c>
+      <c r="D136" s="14">
+        <v>3</v>
+      </c>
+      <c r="E136" s="14"/>
+      <c r="F136" s="14"/>
+      <c r="G136" s="14">
+        <v>0</v>
+      </c>
+      <c r="H136" s="14" t="s">
+        <v>525</v>
+      </c>
+      <c r="I136" s="14">
+        <v>0</v>
+      </c>
+      <c r="J136" s="14">
+        <v>0</v>
+      </c>
+      <c r="K136" s="14" t="s">
+        <v>599</v>
+      </c>
+      <c r="L136" s="14"/>
+      <c r="M136" s="14"/>
+      <c r="N136" s="12"/>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="17">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C137" s="17">
-        <v>1114</v>
+        <v>2</v>
       </c>
       <c r="D137" s="17">
-        <v>2</v>
-      </c>
-      <c r="E137" s="17"/>
-      <c r="F137" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="E137" s="17" t="s">
+        <v>689</v>
+      </c>
+      <c r="F137" s="17" t="s">
+        <v>614</v>
+      </c>
       <c r="G137" s="17">
         <v>0</v>
       </c>
       <c r="H137" s="17" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="I137" s="17">
         <v>0</v>
@@ -10335,24 +10390,28 @@
         <v>0</v>
       </c>
       <c r="K137" s="17" t="s">
-        <v>617</v>
-      </c>
-      <c r="L137" s="17"/>
+        <v>615</v>
+      </c>
+      <c r="L137" s="17" t="s">
+        <v>531</v>
+      </c>
       <c r="M137" s="17"/>
-      <c r="N137" s="12"/>
+      <c r="N137" s="12" t="s">
+        <v>625</v>
+      </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="17">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C138" s="17">
         <v>1114</v>
       </c>
       <c r="D138" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E138" s="17"/>
       <c r="F138" s="17"/>
@@ -10369,100 +10428,98 @@
         <v>0</v>
       </c>
       <c r="K138" s="17" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L138" s="17"/>
       <c r="M138" s="17"/>
       <c r="N138" s="12"/>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A139" s="14">
-        <v>1093</v>
-      </c>
-      <c r="B139" s="14" t="s">
-        <v>679</v>
-      </c>
-      <c r="C139" s="14">
-        <v>0</v>
-      </c>
-      <c r="D139" s="14">
-        <v>999</v>
-      </c>
-      <c r="E139" s="14" t="s">
-        <v>680</v>
-      </c>
-      <c r="F139" s="14" t="s">
-        <v>681</v>
-      </c>
-      <c r="G139" s="14">
-        <v>0</v>
-      </c>
-      <c r="H139" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I139" s="14">
-        <v>0</v>
-      </c>
-      <c r="J139" s="14">
-        <v>1</v>
-      </c>
-      <c r="K139" s="14" t="s">
-        <v>682</v>
-      </c>
-      <c r="L139" s="14" t="s">
-        <v>683</v>
-      </c>
-      <c r="M139" s="12"/>
+      <c r="A139" s="17">
+        <v>1116</v>
+      </c>
+      <c r="B139" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="C139" s="17">
+        <v>1114</v>
+      </c>
+      <c r="D139" s="17">
+        <v>3</v>
+      </c>
+      <c r="E139" s="17"/>
+      <c r="F139" s="17"/>
+      <c r="G139" s="17">
+        <v>0</v>
+      </c>
+      <c r="H139" s="17" t="s">
+        <v>525</v>
+      </c>
+      <c r="I139" s="17">
+        <v>0</v>
+      </c>
+      <c r="J139" s="17">
+        <v>0</v>
+      </c>
+      <c r="K139" s="17" t="s">
+        <v>616</v>
+      </c>
+      <c r="L139" s="17"/>
+      <c r="M139" s="17"/>
       <c r="N139" s="12"/>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="14">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B140" s="14" t="s">
-        <v>256</v>
+        <v>679</v>
       </c>
       <c r="C140" s="14">
-        <v>1093</v>
+        <v>0</v>
       </c>
       <c r="D140" s="14">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="E140" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="F140" s="14"/>
+        <v>680</v>
+      </c>
+      <c r="F140" s="14" t="s">
+        <v>681</v>
+      </c>
       <c r="G140" s="14">
         <v>0</v>
       </c>
       <c r="H140" s="14" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="I140" s="14">
         <v>0</v>
       </c>
       <c r="J140" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K140" s="14" t="s">
-        <v>684</v>
-      </c>
-      <c r="L140" s="14"/>
+        <v>682</v>
+      </c>
+      <c r="L140" s="14" t="s">
+        <v>683</v>
+      </c>
       <c r="M140" s="12"/>
       <c r="N140" s="12"/>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="14">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B141" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C141" s="14">
         <v>1093</v>
       </c>
       <c r="D141" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" s="14" t="s">
         <v>136</v>
@@ -10481,7 +10538,7 @@
         <v>0</v>
       </c>
       <c r="K141" s="14" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="L141" s="14"/>
       <c r="M141" s="12"/>
@@ -10489,16 +10546,16 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="14">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B142" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C142" s="14">
         <v>1093</v>
       </c>
       <c r="D142" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E142" s="14" t="s">
         <v>136</v>
@@ -10517,7 +10574,7 @@
         <v>0</v>
       </c>
       <c r="K142" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="L142" s="14"/>
       <c r="M142" s="12"/>
@@ -10525,16 +10582,16 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="14">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B143" s="14" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C143" s="14">
         <v>1093</v>
       </c>
       <c r="D143" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E143" s="14" t="s">
         <v>136</v>
@@ -10553,24 +10610,24 @@
         <v>0</v>
       </c>
       <c r="K143" s="14" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L143" s="14"/>
       <c r="M143" s="12"/>
       <c r="N143" s="12"/>
     </row>
-    <row r="144" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="14">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C144" s="14">
         <v>1093</v>
       </c>
       <c r="D144" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E144" s="14" t="s">
         <v>136</v>
@@ -10589,74 +10646,72 @@
         <v>0</v>
       </c>
       <c r="K144" s="14" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="L144" s="14"/>
       <c r="M144" s="12"/>
       <c r="N144" s="12"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A145" s="18">
-        <v>1117</v>
-      </c>
-      <c r="B145" s="18" t="s">
-        <v>693</v>
-      </c>
-      <c r="C145" s="18">
-        <v>118</v>
-      </c>
-      <c r="D145" s="18">
-        <v>999</v>
-      </c>
-      <c r="E145" s="18" t="s">
-        <v>703</v>
-      </c>
-      <c r="F145" s="19" t="s">
-        <v>773</v>
-      </c>
-      <c r="G145" s="18">
-        <v>0</v>
-      </c>
-      <c r="H145" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="I145" s="18">
-        <v>0</v>
-      </c>
-      <c r="J145" s="18">
-        <v>0</v>
-      </c>
-      <c r="K145" s="18" t="s">
-        <v>694</v>
-      </c>
-      <c r="L145" s="18" t="s">
-        <v>576</v>
-      </c>
+    <row r="145" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="14">
+        <v>1098</v>
+      </c>
+      <c r="B145" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C145" s="14">
+        <v>1093</v>
+      </c>
+      <c r="D145" s="14">
+        <v>5</v>
+      </c>
+      <c r="E145" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="F145" s="14"/>
+      <c r="G145" s="14">
+        <v>0</v>
+      </c>
+      <c r="H145" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="I145" s="14">
+        <v>0</v>
+      </c>
+      <c r="J145" s="14">
+        <v>0</v>
+      </c>
+      <c r="K145" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="L145" s="14"/>
       <c r="M145" s="12"/>
       <c r="N145" s="12"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="18">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B146" s="18" t="s">
-        <v>256</v>
+        <v>693</v>
       </c>
       <c r="C146" s="18">
-        <v>1117</v>
+        <v>118</v>
       </c>
       <c r="D146" s="18">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="E146" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="F146" s="18"/>
+        <v>703</v>
+      </c>
+      <c r="F146" s="19" t="s">
+        <v>773</v>
+      </c>
       <c r="G146" s="18">
         <v>0</v>
       </c>
       <c r="H146" s="18" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="I146" s="18">
         <v>0</v>
@@ -10665,24 +10720,26 @@
         <v>0</v>
       </c>
       <c r="K146" s="18" t="s">
-        <v>695</v>
-      </c>
-      <c r="L146" s="18"/>
+        <v>694</v>
+      </c>
+      <c r="L146" s="18" t="s">
+        <v>576</v>
+      </c>
       <c r="M146" s="12"/>
       <c r="N146" s="12"/>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="18">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B147" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C147" s="18">
         <v>1117</v>
       </c>
       <c r="D147" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="18" t="s">
         <v>136</v>
@@ -10701,7 +10758,7 @@
         <v>0</v>
       </c>
       <c r="K147" s="18" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="L147" s="18"/>
       <c r="M147" s="12"/>
@@ -10709,16 +10766,16 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="18">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B148" s="18" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C148" s="18">
         <v>1117</v>
       </c>
       <c r="D148" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E148" s="18" t="s">
         <v>136</v>
@@ -10737,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="K148" s="18" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="L148" s="18"/>
       <c r="M148" s="12"/>
@@ -10745,16 +10802,16 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="18">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C149" s="18">
         <v>1117</v>
       </c>
       <c r="D149" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E149" s="18" t="s">
         <v>136</v>
@@ -10773,7 +10830,7 @@
         <v>0</v>
       </c>
       <c r="K149" s="18" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="L149" s="18"/>
       <c r="M149" s="12"/>
@@ -10781,16 +10838,16 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="18">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B150" s="18" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C150" s="18">
         <v>1117</v>
       </c>
       <c r="D150" s="18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E150" s="18" t="s">
         <v>136</v>
@@ -10809,45 +10866,45 @@
         <v>0</v>
       </c>
       <c r="K150" s="18" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="L150" s="18"/>
       <c r="M150" s="12"/>
       <c r="N150" s="12"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A151" s="12">
-        <v>11</v>
-      </c>
-      <c r="B151" s="12" t="s">
-        <v>730</v>
-      </c>
-      <c r="C151" s="12">
-        <v>0</v>
-      </c>
-      <c r="D151" s="12">
-        <v>11</v>
-      </c>
-      <c r="E151" s="12" t="s">
-        <v>770</v>
-      </c>
-      <c r="F151" s="12"/>
-      <c r="G151" s="12">
-        <v>0</v>
-      </c>
-      <c r="H151" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="I151" s="12">
-        <v>0</v>
-      </c>
-      <c r="J151" s="12">
-        <v>0</v>
-      </c>
-      <c r="K151" s="12"/>
-      <c r="L151" s="20" t="s">
-        <v>723</v>
-      </c>
+      <c r="A151" s="18">
+        <v>1122</v>
+      </c>
+      <c r="B151" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="C151" s="18">
+        <v>1117</v>
+      </c>
+      <c r="D151" s="18">
+        <v>5</v>
+      </c>
+      <c r="E151" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="F151" s="18"/>
+      <c r="G151" s="18">
+        <v>0</v>
+      </c>
+      <c r="H151" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I151" s="18">
+        <v>0</v>
+      </c>
+      <c r="J151" s="18">
+        <v>0</v>
+      </c>
+      <c r="K151" s="18" t="s">
+        <v>699</v>
+      </c>
+      <c r="L151" s="18"/>
       <c r="M151" s="12"/>
       <c r="N151" s="12"/>
     </row>
@@ -11155,7 +11212,7 @@
       </c>
       <c r="L160" s="14"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="14">
         <v>123</v>
       </c>
@@ -11187,7 +11244,7 @@
       </c>
       <c r="L161" s="14"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="14">
         <v>124</v>
       </c>
@@ -11219,7 +11276,7 @@
       </c>
       <c r="L162" s="14"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="21">
         <v>1133</v>
       </c>
@@ -11257,7 +11314,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="21">
         <v>1134</v>
       </c>
@@ -11289,7 +11346,7 @@
       </c>
       <c r="L164" s="21"/>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="21">
         <v>1135</v>
       </c>
@@ -11321,7 +11378,7 @@
       </c>
       <c r="L165" s="21"/>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" s="21">
         <v>1136</v>
       </c>
@@ -11353,7 +11410,7 @@
       </c>
       <c r="L166" s="21"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="21">
         <v>1137</v>
       </c>
@@ -11385,7 +11442,7 @@
       </c>
       <c r="L167" s="21"/>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="14">
         <v>1138</v>
       </c>
@@ -11423,7 +11480,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="14">
         <v>1139</v>
       </c>
@@ -11459,7 +11516,7 @@
       </c>
       <c r="L169" s="14"/>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" s="14">
         <v>1140</v>
       </c>
@@ -11491,7 +11548,7 @@
       </c>
       <c r="L170" s="14"/>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="14">
         <v>1141</v>
       </c>
@@ -11523,7 +11580,7 @@
       </c>
       <c r="L171" s="14"/>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="14">
         <v>1143</v>
       </c>
@@ -11555,7 +11612,7 @@
       </c>
       <c r="L172" s="14"/>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="14">
         <v>1144</v>
       </c>
@@ -11587,7 +11644,7 @@
       </c>
       <c r="L173" s="14"/>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" s="14">
         <v>1145</v>
       </c>
@@ -11619,7 +11676,7 @@
       </c>
       <c r="L174" s="14"/>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" s="14">
         <v>1146</v>
       </c>
@@ -11657,28 +11714,157 @@
         <v>780</v>
       </c>
     </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A176" s="20">
+        <v>125</v>
+      </c>
+      <c r="B176" s="20" t="s">
+        <v>800</v>
+      </c>
+      <c r="C176" s="20">
+        <v>11</v>
+      </c>
+      <c r="D176" s="20">
+        <v>0</v>
+      </c>
+      <c r="E176" s="20" t="s">
+        <v>810</v>
+      </c>
+      <c r="F176" s="20" t="s">
+        <v>808</v>
+      </c>
+      <c r="G176" s="20"/>
+      <c r="H176" s="20" t="s">
+        <v>811</v>
+      </c>
+      <c r="I176" s="14">
+        <v>0</v>
+      </c>
+      <c r="J176" s="14">
+        <v>0</v>
+      </c>
+      <c r="K176" s="20" t="s">
+        <v>801</v>
+      </c>
+      <c r="L176" s="20" t="s">
+        <v>813</v>
+      </c>
+      <c r="O176" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A177" s="20">
+        <v>126</v>
+      </c>
+      <c r="B177" s="20" t="s">
+        <v>805</v>
+      </c>
+      <c r="C177" s="20">
+        <v>125</v>
+      </c>
+      <c r="D177" s="20">
+        <v>1</v>
+      </c>
+      <c r="E177" s="20"/>
+      <c r="F177" s="20"/>
+      <c r="G177" s="20"/>
+      <c r="H177" s="20" t="s">
+        <v>812</v>
+      </c>
+      <c r="I177" s="14">
+        <v>0</v>
+      </c>
+      <c r="J177" s="14">
+        <v>0</v>
+      </c>
+      <c r="K177" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="L177" s="20"/>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A178" s="20">
+        <v>127</v>
+      </c>
+      <c r="B178" s="20" t="s">
+        <v>806</v>
+      </c>
+      <c r="C178" s="20">
+        <v>125</v>
+      </c>
+      <c r="D178" s="20">
+        <v>2</v>
+      </c>
+      <c r="E178" s="20"/>
+      <c r="F178" s="20"/>
+      <c r="G178" s="20"/>
+      <c r="H178" s="20" t="s">
+        <v>812</v>
+      </c>
+      <c r="I178" s="14">
+        <v>0</v>
+      </c>
+      <c r="J178" s="14">
+        <v>0</v>
+      </c>
+      <c r="K178" s="20" t="s">
+        <v>803</v>
+      </c>
+      <c r="L178" s="20"/>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A179" s="20">
+        <v>128</v>
+      </c>
+      <c r="B179" s="20" t="s">
+        <v>807</v>
+      </c>
+      <c r="C179" s="20">
+        <v>125</v>
+      </c>
+      <c r="D179" s="20">
+        <v>3</v>
+      </c>
+      <c r="E179" s="20"/>
+      <c r="F179" s="20"/>
+      <c r="G179" s="20"/>
+      <c r="H179" s="20" t="s">
+        <v>812</v>
+      </c>
+      <c r="I179" s="14">
+        <v>0</v>
+      </c>
+      <c r="J179" s="14">
+        <v>0</v>
+      </c>
+      <c r="K179" s="20" t="s">
+        <v>804</v>
+      </c>
+      <c r="L179" s="20"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A125" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:A126" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A16:A25">
+  <conditionalFormatting sqref="A17:A26">
     <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A139:A150">
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+  <conditionalFormatting sqref="A27:A139 A1:A11 A152:A1048576">
+    <cfRule type="duplicateValues" dxfId="10" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A10 A26:A138 A151:A1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+  <conditionalFormatting sqref="A140:A151">
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C131">
+  <conditionalFormatting sqref="C132">
     <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C132">
+  <conditionalFormatting sqref="C133">
     <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C137">
+  <conditionalFormatting sqref="C138">
     <cfRule type="duplicateValues" dxfId="6" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C138">
+  <conditionalFormatting sqref="C139">
     <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L153:L156 B153:J156">

--- a/ZR.Admin.WebApi/wwwroot/data.xlsx
+++ b/ZR.Admin.WebApi/wwwroot/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Mine\ZRAdmin\public\ZrAdminNet\ZR.Admin.WebApi\wwwroot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E873AE01-F10A-4CF2-B1A2-8F8804A50585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A36FFB0-D970-4C8D-8BC6-A0E74F167FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="849" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="849" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="user" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="825">
   <si>
     <t>系统管理</t>
   </si>
@@ -2810,6 +2810,34 @@
   </si>
   <si>
     <t>sys.account.passwordExpireDay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件分组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fileGroup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tool/file/fileGroup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>filegroup:list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>filegroup:delete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>filegroup:update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tree-table</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5398,7 +5426,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O179"/>
+  <dimension ref="A1:O182"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.44140625" customWidth="1"/>
@@ -11840,7 +11868,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="20">
         <v>126</v>
       </c>
@@ -11870,7 +11898,7 @@
       </c>
       <c r="L177" s="20"/>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="20">
         <v>127</v>
       </c>
@@ -11900,7 +11928,7 @@
       </c>
       <c r="L178" s="20"/>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="20">
         <v>128</v>
       </c>
@@ -11929,6 +11957,118 @@
         <v>804</v>
       </c>
       <c r="L179" s="20"/>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A180" s="12">
+        <v>1147</v>
+      </c>
+      <c r="B180" s="12" t="s">
+        <v>818</v>
+      </c>
+      <c r="C180" s="12">
+        <v>3</v>
+      </c>
+      <c r="D180" s="12">
+        <v>17</v>
+      </c>
+      <c r="E180" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="F180" s="12" t="s">
+        <v>820</v>
+      </c>
+      <c r="G180" s="12">
+        <v>0</v>
+      </c>
+      <c r="H180" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I180" s="12">
+        <v>0</v>
+      </c>
+      <c r="J180" s="12">
+        <v>0</v>
+      </c>
+      <c r="K180" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="L180" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="M180" s="12"/>
+      <c r="N180" s="12"/>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A181" s="12">
+        <v>1150</v>
+      </c>
+      <c r="B181" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C181" s="12">
+        <v>1147</v>
+      </c>
+      <c r="D181" s="12">
+        <v>3</v>
+      </c>
+      <c r="E181" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F181" s="12"/>
+      <c r="G181" s="12">
+        <v>0</v>
+      </c>
+      <c r="H181" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I181" s="12">
+        <v>0</v>
+      </c>
+      <c r="J181" s="12">
+        <v>0</v>
+      </c>
+      <c r="K181" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="L181" s="12"/>
+      <c r="M181" s="12"/>
+      <c r="N181" s="12"/>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A182" s="12">
+        <v>1151</v>
+      </c>
+      <c r="B182" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C182" s="12">
+        <v>1147</v>
+      </c>
+      <c r="D182" s="12">
+        <v>4</v>
+      </c>
+      <c r="E182" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F182" s="12"/>
+      <c r="G182" s="12">
+        <v>0</v>
+      </c>
+      <c r="H182" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I182" s="12">
+        <v>0</v>
+      </c>
+      <c r="J182" s="12">
+        <v>0</v>
+      </c>
+      <c r="K182" s="12" t="s">
+        <v>823</v>
+      </c>
+      <c r="L182" s="12"/>
+      <c r="M182" s="12"/>
+      <c r="N182" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:A126" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
